--- a/Form.xlsx
+++ b/Form.xlsx
@@ -44,13 +44,13 @@
     <t>est 2</t>
   </si>
   <si>
-    <t>Address</t>
+    <t>XUHIHOIOPAKX</t>
   </si>
   <si>
     <t>test Adrr</t>
   </si>
   <si>
-    <t>aaaaaaadd</t>
+    <t>xa84x89a3x8ax4</t>
   </si>
 </sst>
 </file>
@@ -58,7 +58,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -70,6 +70,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -108,7 +114,7 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -432,7 +438,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>8</v>
